--- a/src/main/resources/reports/apk_5.xlsx
+++ b/src/main/resources/reports/apk_5.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="5.1" sheetId="1" state="visible" r:id="rId2"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="81">
   <si>
     <t xml:space="preserve">Наименование показателя</t>
   </si>
@@ -118,9 +118,6 @@
   <si>
     <t xml:space="preserve">в том числе:
 рабочие постоянные</t>
-  </si>
-  <si>
-    <t xml:space="preserve">сами</t>
   </si>
   <si>
     <t xml:space="preserve">из них: 
@@ -195,6 +192,7 @@
         <color rgb="FF1C1C1C"/>
         <rFont val="JetBrains Mono"/>
         <family val="3"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">totalAmount</t>
     </r>
@@ -297,8 +295,8 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val=""/>
-        <family val="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">${expense_52410.</t>
@@ -309,6 +307,7 @@
         <color rgb="FF1C1C1C"/>
         <rFont val="JetBrains Mono"/>
         <family val="3"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">totalAmount</t>
     </r>
@@ -316,8 +315,8 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val=""/>
-        <family val="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">}</t>
@@ -350,6 +349,7 @@
         <color rgb="FF1C1C1C"/>
         <rFont val="JetBrains Mono"/>
         <family val="3"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">totalAmount</t>
     </r>
@@ -384,6 +384,7 @@
         <color rgb="FF1C1C1C"/>
         <rFont val="JetBrains Mono"/>
         <family val="3"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">totalAmount</t>
     </r>
@@ -424,6 +425,7 @@
         <color rgb="FF1C1C1C"/>
         <rFont val="JetBrains Mono"/>
         <family val="3"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">totalAmount</t>
     </r>
@@ -573,6 +575,7 @@
       <color rgb="FF1C1C1C"/>
       <name val="JetBrains Mono"/>
       <family val="3"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -590,12 +593,12 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val=""/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -604,20 +607,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC5E0B4"/>
-        <bgColor rgb="FFAFD095"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFD095"/>
-        <bgColor rgb="FFC5E0B4"/>
       </patternFill>
     </fill>
   </fills>
@@ -676,7 +667,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="46">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -749,11 +740,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="4" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -761,11 +748,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="6" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -773,19 +760,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -793,38 +772,42 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -841,10 +824,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -855,10 +834,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -902,7 +877,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFAFD095"/>
+      <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -922,7 +897,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFC5E0B4"/>
+      <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -1053,140 +1028,136 @@
       <c r="B5" s="15" t="n">
         <v>51110</v>
       </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="9" t="s">
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+    </row>
+    <row r="6" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="19" t="s">
         <v>8</v>
-      </c>
-      <c r="G5" s="9"/>
-    </row>
-    <row r="6" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
-        <v>9</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>51111</v>
       </c>
       <c r="C6" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="E6" s="18"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="s">
         <v>11</v>
-      </c>
-      <c r="E6" s="19"/>
-      <c r="F6" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="9"/>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
-        <v>12</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>51112</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="19"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="18"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
-        <v>13</v>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="19" t="s">
+        <v>12</v>
       </c>
       <c r="B8" s="15" t="n">
         <v>51113</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="19"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="18"/>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
-        <v>14</v>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19" t="s">
+        <v>13</v>
       </c>
       <c r="B9" s="15" t="n">
         <v>51114</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
-        <v>15</v>
+      <c r="C9" s="20"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="s">
+        <v>14</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>51115</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
-        <v>16</v>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>51116</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
-        <v>17</v>
+      <c r="C11" s="20"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19" t="s">
+        <v>16</v>
       </c>
       <c r="B12" s="15" t="n">
         <v>51117</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
-        <v>18</v>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>17</v>
       </c>
       <c r="B13" s="15" t="n">
         <v>51118</v>
       </c>
-      <c r="C13" s="24"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C13" s="23"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" s="15" t="n">
         <v>51120</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="20"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" s="15" t="n">
         <v>51130</v>
@@ -1199,73 +1170,67 @@
         <f aca="false">D16+D17</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E15" s="26" t="str">
+      <c r="E15" s="18" t="str">
         <f aca="false">E17</f>
         <v>${expense_52600.totalAmount}</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>8</v>
-      </c>
+      <c r="F15" s="9"/>
       <c r="G15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="s">
-        <v>21</v>
+      <c r="A16" s="19" t="s">
+        <v>20</v>
       </c>
       <c r="B16" s="15" t="n">
         <v>51131</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="28" t="s">
+      <c r="E16" s="18"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+    </row>
+    <row r="17" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="s">
         <v>23</v>
-      </c>
-      <c r="E16" s="19"/>
-      <c r="F16" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="G16" s="9"/>
-    </row>
-    <row r="17" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="s">
-        <v>24</v>
       </c>
       <c r="B17" s="15" t="n">
         <v>51132</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="E17" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>8</v>
-      </c>
+      <c r="F17" s="9"/>
       <c r="G17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18" s="15" t="n">
         <v>51140</v>
       </c>
-      <c r="C18" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
+      <c r="C18" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="20"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
     </row>
     <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" s="15" t="n">
         <v>51200</v>
@@ -1278,125 +1243,121 @@
         <f aca="false">D20</f>
         <v>${technologist.totalSalary}</v>
       </c>
-      <c r="E19" s="19"/>
-      <c r="F19" s="9" t="s">
-        <v>8</v>
-      </c>
+      <c r="E19" s="18"/>
+      <c r="F19" s="9"/>
       <c r="G19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B20" s="15" t="n">
         <v>51210</v>
       </c>
       <c r="C20" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="19"/>
-      <c r="F20" s="9" t="s">
-        <v>8</v>
-      </c>
+      <c r="E20" s="18"/>
+      <c r="F20" s="9"/>
       <c r="G20" s="9"/>
     </row>
     <row r="21" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="15" t="n">
         <v>51300</v>
       </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="19"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="18"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" s="15" t="n">
         <v>51400</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="19"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="18"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
     </row>
     <row r="23" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" s="15" t="n">
         <v>51500</v>
       </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="19"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="18"/>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="15" t="n">
         <v>51600</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="19"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="18"/>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="15" t="n">
         <v>51700</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="19"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="18"/>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="31"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="33"/>
+      <c r="A26" s="28"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="30"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="31"/>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
+      <c r="A27" s="28"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="34"/>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="32"/>
+      <c r="A28" s="31"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="29"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G29" s="35"/>
+      <c r="G29" s="32"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1453,504 +1414,482 @@
   <dimension ref="A1:H46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="36" width="76.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="36" width="11.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="36" width="19.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="36" width="29.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="36" width="20.25"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="6" style="36" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="33" width="76.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="33" width="11.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="33" width="19.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="33" width="29.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="33" width="20.25"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="6" style="33" width="9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
+        <v>38</v>
+      </c>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="38" t="n">
+      <c r="A2" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38" t="n">
+      <c r="B2" s="36"/>
+      <c r="C2" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="39" t="n">
+      <c r="D2" s="37" t="n">
         <v>3</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
-      <c r="G2" s="37"/>
+      <c r="G2" s="35"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>52110</v>
       </c>
-      <c r="D3" s="41"/>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="40"/>
+      <c r="D3" s="39"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="38"/>
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>52120</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="44" t="s">
-        <v>44</v>
-      </c>
       <c r="B5" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>52200</v>
       </c>
-      <c r="D5" s="45"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>52300</v>
       </c>
-      <c r="D6" s="42" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>8</v>
-      </c>
+      <c r="D6" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>52310</v>
       </c>
-      <c r="D7" s="46" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>8</v>
-      </c>
+      <c r="D7" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>52400</v>
       </c>
-      <c r="D8" s="42" t="e">
+      <c r="D8" s="39" t="e">
         <f aca="false">D9+D11+D12+D15</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
     </row>
     <row r="9" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>52410</v>
       </c>
-      <c r="D9" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
+      <c r="D9" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>52411</v>
       </c>
-      <c r="D10" s="45"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="36" t="s">
-        <v>55</v>
+      <c r="D10" s="39"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="33" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>52420</v>
       </c>
-      <c r="D11" s="42" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
+      <c r="D11" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>52430</v>
       </c>
-      <c r="D12" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
+      <c r="D12" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>52440</v>
       </c>
-      <c r="D13" s="45"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
     </row>
     <row r="14" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>52450</v>
       </c>
-      <c r="D14" s="45"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>52490</v>
       </c>
-      <c r="D15" s="48" t="s">
+      <c r="D15" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+    </row>
+    <row r="16" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-    </row>
-    <row r="16" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="44" t="s">
+      <c r="B16" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>52500</v>
       </c>
-      <c r="D16" s="45"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="44" t="s">
-        <v>66</v>
+      <c r="A17" s="41" t="s">
+        <v>65</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>52600</v>
       </c>
-      <c r="D17" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
+      <c r="D17" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
     </row>
     <row r="18" customFormat="false" ht="85.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="44" t="s">
+      <c r="A18" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>52700</v>
       </c>
-      <c r="D18" s="42" t="e">
+      <c r="D18" s="39" t="e">
         <f aca="false">D19+D25+D28</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
     </row>
     <row r="19" customFormat="false" ht="84.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>52701</v>
       </c>
-      <c r="D19" s="46" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
+      <c r="D19" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
     </row>
     <row r="20" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>52702</v>
       </c>
-      <c r="D20" s="45"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
     </row>
     <row r="21" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>52703</v>
       </c>
-      <c r="D21" s="45"/>
+      <c r="D21" s="39"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>52704</v>
       </c>
-      <c r="D22" s="44"/>
+      <c r="D22" s="42"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
     </row>
     <row r="23" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>52705</v>
       </c>
-      <c r="D23" s="45"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="43"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
     </row>
     <row r="24" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>52706</v>
       </c>
-      <c r="D24" s="45"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
     </row>
     <row r="25" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>52707</v>
       </c>
-      <c r="D25" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="E25" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
+      <c r="D25" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
     </row>
     <row r="26" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>52708</v>
       </c>
-      <c r="D26" s="44"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35"/>
     </row>
     <row r="27" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>52709</v>
       </c>
-      <c r="D27" s="44"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
     </row>
     <row r="28" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>52710</v>
       </c>
-      <c r="D28" s="46" t="s">
-        <v>81</v>
-      </c>
-      <c r="E28" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
+      <c r="D28" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5"/>
-      <c r="B29" s="49"/>
+      <c r="B29" s="45"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
-      <c r="E29" s="37"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="37"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="43"/>
-      <c r="B30" s="43"/>
-      <c r="C30" s="43"/>
+      <c r="A30" s="40"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="43"/>
-      <c r="B31" s="43"/>
-      <c r="C31" s="43"/>
+      <c r="A31" s="40"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="40"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="43"/>
-      <c r="B32" s="43"/>
-      <c r="C32" s="43"/>
+      <c r="A32" s="40"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9"/>
